--- a/sheet/ItemCardData.xlsx
+++ b/sheet/ItemCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9222D96-EF27-4ED3-A4C7-B2CAF37B0C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8C8C5F-4D8B-472B-8E2E-C7A8443612AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5940" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,10 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选择：①重抽任意张手牌，然后可以将一张横置的升级牌复位。②消耗1时间，重抽房间区任意牌，将备战区所有牌加入手牌，然后重整。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>木柴捆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,10 +143,6 @@
   </si>
   <si>
     <t>弹药</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择：①将法术表中的法术牌洗混，然后从中抽1张牌，适用其效果。②翻开法术牌堆顶的1张牌，适用其效果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -160,6 +152,22 @@
   <si>
     <t>在道具牌区时，玩家手牌基数减1。&lt;br&gt;
 被弃置时，玩家将手牌补满，或抽3张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择：取出升级牌堆顶的3张法术牌，选1张适用其效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择：①重抽任意张手牌，并回复1HP。②消耗1时间，将备战区所有牌加入手牌，然后重整，之后回复一半HP（向下取整）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能使用。因《商店》牌的效果被弃置时，额外获得1金币。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -502,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="32.125" customWidth="1"/>
@@ -517,7 +525,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -534,135 +542,148 @@
     </row>
     <row r="2" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="57" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="E4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="57" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
+    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/ItemCardData.xlsx
+++ b/sheet/ItemCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8C8C5F-4D8B-472B-8E2E-C7A8443612AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B104AC48-703C-48D3-9B7D-0F6811C44157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="3255" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8130" yWindow="3390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,10 +143,6 @@
   </si>
   <si>
     <t>弹药</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水晶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -168,6 +164,20 @@
   </si>
   <si>
     <t>不能使用。因《商店》牌的效果被弃置时，额外获得1金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹匣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以至多将3张“弹药”牌叠放在本牌下方。&lt;br&gt;
+可以主动弃置本牌。&lt;br&gt;
+被弃置时，获得本牌下方叠放的所有牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔瓶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -510,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="32.125" customWidth="1"/>
@@ -557,13 +567,13 @@
     </row>
     <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E3" s="2"/>
       <c r="G3" s="2"/>
@@ -591,7 +601,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
@@ -606,42 +616,44 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -684,6 +696,17 @@
       </c>
       <c r="D12" s="1" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/ItemCardData.xlsx
+++ b/sheet/ItemCardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B104AC48-703C-48D3-9B7D-0F6811C44157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D395C09-0E53-433B-AA0C-F58E5E8BDDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8130" yWindow="3390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,14 +78,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cursed pot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>诅咒之壶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Pot</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -98,34 +90,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Pouch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钱袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tags</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>从法术牌堆抽3张牌，选其中1张加入法术表。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得1金币，可以额外弃置任意张同名牌，每额外弃置1张同名牌，额外获得2金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复1MP，可以额外弃置任意张同名牌，每额外弃置1张同名牌，额外回复2MP。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>未知卷轴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -134,50 +102,66 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选择上下左右中的一个方向，那个方向上所有房间中各选1张在对侧的怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择同一行或同一列中1张怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>弹药</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在道具牌区时，玩家手牌基数减1。&lt;br&gt;
-被弃置时，玩家将手牌补满，或抽3张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择：取出升级牌堆顶的3张法术牌，选1张适用其效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择：①重抽任意张手牌，并回复1HP。②消耗1时间，将备战区所有牌加入手牌，然后重整，之后回复一半HP（向下取整）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>金块</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不能使用。因《商店》牌的效果被弃置时，额外获得1金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>弹匣</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>魔瓶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>可以至多将3张“弹药”牌叠放在本牌下方。&lt;br&gt;
-可以主动弃置本牌。&lt;br&gt;
+可以随时弃置本牌。&lt;br&gt;
 被弃置时，获得本牌下方叠放的所有牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>魔瓶</t>
+    <t>回复1MP。如果堆叠，堆叠中每有1张牌，额外回复2MP。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从升级牌堆翻开前3张法术牌，选其中1张加入法术表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔典</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择同一行或同一列中1张其他怪物牌，使其点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只能由点数为2以上的牌使用。选择上下左右中的一个方向，那个方向上所有房间各选1张怪物牌，使其点数减1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择：①重抽任意张手牌，并回复1HP。②消耗1时间，重整，然后将备战区所有牌加入手牌，并回复一半HP（向下取整）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只能由点数为2以上的牌使用。选择同一行或同一列中1个其他房间，使该房间的所有牌点数减2。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能使用。&lt;br&gt;
+出售时，价值2金币。堆叠时，堆叠中每有1张牌，价值增加4金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从升级牌堆翻开第1张法术牌，然后可以适用其效果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="32.125" customWidth="1"/>
@@ -535,7 +519,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -552,161 +536,145 @@
     </row>
     <row r="2" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="2"/>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>14</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="57" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="57" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>34</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
+      <c r="C9" t="s">
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="57" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/ItemCardData.xlsx
+++ b/sheet/ItemCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D395C09-0E53-433B-AA0C-F58E5E8BDDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557C0BD0-1FCA-4CAA-ABEB-0A49D9903AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -118,16 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可以至多将3张“弹药”牌叠放在本牌下方。&lt;br&gt;
-可以随时弃置本牌。&lt;br&gt;
-被弃置时，获得本牌下方叠放的所有牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复1MP。如果堆叠，堆叠中每有1张牌，额外回复2MP。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>从升级牌堆翻开前3张法术牌，选其中1张加入法术表。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,12 +146,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>从升级牌堆翻开第1张法术牌，然后可以适用其效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>不能使用。&lt;br&gt;
-出售时，价值2金币。堆叠时，堆叠中每有1张牌，价值增加4金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从升级牌堆翻开第1张法术牌，然后可以适用其效果。</t>
+出售时，价值2金币。可堆叠出售，堆叠中每多1张牌，价值增加4金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复1MP。可堆叠使用，堆叠中每多1张牌，额外回复2MP。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正置时，可以将至多3张“弹药”牌堆叠在本牌下方。&lt;br&gt;
+可以随时横置本牌。&lt;br&gt;
+横置时，可以将堆叠的牌取出。横置的本牌没有堆叠其他牌时，弃置本牌。&lt;br&gt;
+被弃置时，将堆叠的所有牌一并弃置。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -542,7 +543,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="2"/>
@@ -570,7 +571,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="3"/>
@@ -583,20 +584,20 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -607,7 +608,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -626,7 +627,7 @@
     </row>
     <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -635,7 +636,7 @@
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" x14ac:dyDescent="0.2">
@@ -649,7 +650,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
@@ -663,10 +664,10 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="114" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -674,7 +675,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/ItemCardData.xlsx
+++ b/sheet/ItemCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557C0BD0-1FCA-4CAA-ABEB-0A49D9903AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DC2DD6-7EB3-4E70-AF99-6A696CFE7DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="3735" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,18 +62,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>吹箭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标枪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>石子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>木柴捆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -98,71 +86,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选同房间中1张怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弹药</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>金块</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>弹匣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>魔瓶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>从升级牌堆翻开前3张法术牌，选其中1张加入法术表。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔典</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择同一行或同一列中1张其他怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只能由点数为2以上的牌使用。选择上下左右中的一个方向，那个方向上所有房间各选1张怪物牌，使其点数减1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>巨石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择：①重抽任意张手牌，并回复1HP。②消耗1时间，重整，然后将备战区所有牌加入手牌，并回复一半HP（向下取整）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只能由点数为2以上的牌使用。选择同一行或同一列中1个其他房间，使该房间的所有牌点数减2。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从升级牌堆翻开第1张法术牌，然后可以适用其效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不能使用。&lt;br&gt;
-出售时，价值2金币。可堆叠出售，堆叠中每多1张牌，价值增加4金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复1MP。可堆叠使用，堆叠中每多1张牌，额外回复2MP。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正置时，可以将至多3张“弹药”牌堆叠在本牌下方。&lt;br&gt;
-可以随时横置本牌。&lt;br&gt;
-横置时，可以将堆叠的牌取出。横置的本牌没有堆叠其他牌时，弃置本牌。&lt;br&gt;
-被弃置时，将堆叠的所有牌一并弃置。</t>
+出售时，价值2金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择：①重抽任意张手牌。②消耗1时间，重置探索区，并回复一半HP和一半MP。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复1MP。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻开升级牌堆前3张法术牌，选其中1张适用效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绷带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复1HP。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量药水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚弱药水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使楼层区1张怪物牌点数加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使楼层区1张怪物牌点数减1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -505,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="32.125" customWidth="1"/>
@@ -520,7 +489,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -535,147 +504,104 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="57" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="114" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/ItemCardData.xlsx
+++ b/sheet/ItemCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DC2DD6-7EB3-4E70-AF99-6A696CFE7DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B4BEFE-331F-467F-9687-8D38494B7FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,10 +75,6 @@
   </si>
   <si>
     <t>壶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tags</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -474,14 +470,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="32.125" customWidth="1"/>
-    <col min="6" max="6" width="62.5" customWidth="1"/>
+    <col min="3" max="3" width="32.125" customWidth="1"/>
+    <col min="5" max="5" width="62.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,119 +485,116 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
